--- a/StructureDefinition-enable-anc-patient.xlsx
+++ b/StructureDefinition-enable-anc-patient.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T16:14:48+00:00</t>
+    <t>2026-07-07T17:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Norwegian Institute of Public Health (NIPH)</t>
+    <t>Devotta</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Norwegian Institute of Public Health (NIPH) (https://www.fhi.no/, johan@devotta.no)</t>
+    <t>Devotta (https://www.devotta.no/, johan@devotta.no)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -738,7 +738,7 @@
 </t>
   </si>
   <si>
-    <t>Optional. Send ONLY if your data-sharing rules permit — the middleware and SMS gateway do not require a name.</t>
+    <t>Optional. Send ONLY if your data-sharing rules permit; the middleware and SMS gateway do not require a name.</t>
   </si>
   <si>
     <t>A name associated with the individual.</t>
